--- a/编程/数据集/第二题整合数据.xlsx
+++ b/编程/数据集/第二题整合数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\数模校赛\Mm\编程\数据集\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D15A4D31-4A6D-4506-99C2-260AD40B6A96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D2DF07E-6BA3-4644-BA48-69F6B769230B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -467,7 +467,7 @@
     <col min="7" max="7" width="23.109375" customWidth="1"/>
     <col min="8" max="8" width="21.44140625" customWidth="1"/>
     <col min="9" max="9" width="19.77734375" customWidth="1"/>
-    <col min="10" max="10" width="16.77734375" customWidth="1"/>
+    <col min="10" max="10" width="20.5546875" customWidth="1"/>
     <col min="11" max="11" width="18.88671875" customWidth="1"/>
   </cols>
   <sheetData>

--- a/编程/数据集/第二题整合数据.xlsx
+++ b/编程/数据集/第二题整合数据.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\数模校赛\Mm\编程\数据集\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D2DF07E-6BA3-4644-BA48-69F6B769230B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4767DC5-BE7C-47A9-ADDF-8647557F552B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5448" yWindow="5100" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -461,7 +461,7 @@
     <col min="1" max="1" width="15.77734375" customWidth="1"/>
     <col min="2" max="2" width="20.6640625" customWidth="1"/>
     <col min="3" max="3" width="25.6640625" customWidth="1"/>
-    <col min="4" max="4" width="17.5546875" customWidth="1"/>
+    <col min="4" max="4" width="21.88671875" customWidth="1"/>
     <col min="5" max="5" width="17.77734375" customWidth="1"/>
     <col min="6" max="6" width="19.21875" customWidth="1"/>
     <col min="7" max="7" width="23.109375" customWidth="1"/>
